--- a/Study/Results/UES/UES.xlsx
+++ b/Study/Results/UES/UES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laila\Desktop\XAMPP\htdocs\Bachelorarbeit\Study\Results\UES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EDA9951-3409-4676-BC1E-5D078E1A2AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36988A1F-5B60-4849-AC72-18FE9EB3F3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Enter your probID</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>mean</t>
+  </si>
+  <si>
+    <t>SD</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1281,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1553,7 +1556,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>20</v>
       </c>
@@ -1573,9 +1576,35 @@
         <f>AVERAGE(Table1[Reward])</f>
         <v>3.9560000000000004</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="G18">
+        <f>AVERAGE(Table1[[Focused Attention]:[Reward]])</f>
+        <v>3.7948333333333317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <f>_xlfn.STDEV.S(Table1[Focused Attention])</f>
+        <v>0.68407880359195528</v>
+      </c>
+      <c r="C19">
+        <f>_xlfn.STDEV.S(Table1[Perceived Usability])</f>
+        <v>0.58690065680009074</v>
+      </c>
+      <c r="D19">
+        <f>_xlfn.STDEV.S(Table1[Aesthetic Appeal])</f>
+        <v>0.80612358735818879</v>
+      </c>
+      <c r="E19">
+        <f>_xlfn.STDEV.S(Table1[Reward])</f>
+        <v>0.73397936911449213</v>
+      </c>
+      <c r="G19">
+        <f>_xlfn.STDEV.S(Table1[[Focused Attention]:[Reward]])</f>
+        <v>0.71361930616001745</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
